--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://record909-my.sharepoint.com/personal/amr_sanad_re-cord_org/Documents/amr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E9431B2-1919-4A80-A67A-5A2C0089B60B}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
   </bookViews>
@@ -39,108 +39,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>AI.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IFX.DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LONN.SW</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HOLN.SW</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ENGI.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAN.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALC.SW</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIO.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ADS.DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AMS.MC</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> UCB.BR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DG.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HEI.DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAND.ST</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ASM.AS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOKIA.HE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HLN.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SGO.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ML.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> KNEBV.HE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DSY.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HEN3.DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EQNR.OL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ENI.MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VWS.CP</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> STMPA.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HLMA.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MRK.DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> INF.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ESSITY-B.ST</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AAL.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DSM.AS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SDZ.SW</t>
+    <t>SDZNY</t>
   </si>
 </sst>
 </file>
@@ -512,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE15FF02-FA5F-4B38-AD88-014FE2510093}">
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.75">
@@ -525,172 +429,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A34" t="s">
-        <v>33</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008AE3B3EDB90C1F40A59126B8CDC80D43" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d1058065e7477b9d5077457695db4452">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="08f2707e77d3c1c984faf87c8023d60a" ns3:_="">
     <xsd:import namespace="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
@@ -878,15 +631,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -896,6 +640,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B8DD49-09CB-47DE-8251-F67EE41634AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -913,14 +665,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
   <ds:schemaRefs>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://record909-my.sharepoint.com/personal/amr_sanad_re-cord_org/Documents/amr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E9431B2-1919-4A80-A67A-5A2C0089B60B}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C7CD5C4-A96D-429B-8DDC-2C77B00F79F9}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
+    <workbookView xWindow="2160" yWindow="2160" windowWidth="14400" windowHeight="8190" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <t>Ticker</t>
   </si>
   <si>
-    <t>SDZNY</t>
+    <t>TSLA</t>
   </si>
 </sst>
 </file>
@@ -435,15 +435,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008AE3B3EDB90C1F40A59126B8CDC80D43" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d1058065e7477b9d5077457695db4452">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="08f2707e77d3c1c984faf87c8023d60a" ns3:_="">
     <xsd:import namespace="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
@@ -631,6 +622,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -640,14 +640,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B8DD49-09CB-47DE-8251-F67EE41634AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -665,6 +657,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
   <ds:schemaRefs>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://record909-my.sharepoint.com/personal/amr_sanad_re-cord_org/Documents/amr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C7CD5C4-A96D-429B-8DDC-2C77B00F79F9}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F63239C8-27F2-5F34-AB57-1B905252AEBE}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="2160" windowWidth="14400" windowHeight="8190" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
+    <workbookView xWindow="2495" yWindow="2495" windowWidth="14400" windowHeight="8190" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,108 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>TSLA</t>
+    <t>AI.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> IFX.DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LONN.SW</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HOLN.SW</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ENGI.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SAN.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ALC.SW</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RIO.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ADS.DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AMS.MC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> UCB.BR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DG.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HEI.DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SAND.ST</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ASM.AS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NOKIA.HE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HLN.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SGO.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ML.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KNEBV.HE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DSY.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HEN3.DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EQNR.OL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ENI.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VWS.CP</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> STMPA.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HLMA.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MRK.DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> INF.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ESSITY-B.ST</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AAL.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DSM.AS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SDZ.SW</t>
   </si>
 </sst>
 </file>
@@ -97,6 +193,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -416,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE15FF02-FA5F-4B38-AD88-014FE2510093}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.75">
@@ -427,6 +527,166 @@
     <row r="2" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A34" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -623,20 +883,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -658,14 +918,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -679,4 +931,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://record909-my.sharepoint.com/personal/amr_sanad_re-cord_org/Documents/amr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F63239C8-27F2-5F34-AB57-1B905252AEBE}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0D30A93-767F-450B-8746-1E6CA09299B1}"/>
   <bookViews>
-    <workbookView xWindow="2495" yWindow="2495" windowWidth="14400" windowHeight="8190" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
+    <workbookView xWindow="2830" yWindow="2830" windowWidth="14400" windowHeight="8190" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Ticker</t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t xml:space="preserve"> SDZ.SW</t>
+  </si>
+  <si>
+    <t>TSLA</t>
   </si>
 </sst>
 </file>
@@ -193,10 +196,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -516,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE15FF02-FA5F-4B38-AD88-014FE2510093}">
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.75">
@@ -526,166 +525,171 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A35" t="s">
         <v>33</v>
       </c>
     </row>
@@ -695,6 +699,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008AE3B3EDB90C1F40A59126B8CDC80D43" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d1058065e7477b9d5077457695db4452">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="08f2707e77d3c1c984faf87c8023d60a" ns3:_="">
     <xsd:import namespace="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
@@ -882,24 +903,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B8DD49-09CB-47DE-8251-F67EE41634AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -915,28 +943,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://record909-my.sharepoint.com/personal/amr_sanad_re-cord_org/Documents/amr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0D30A93-767F-450B-8746-1E6CA09299B1}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19582FC5-95DB-4811-A2C1-F90FC952C57C}"/>
   <bookViews>
-    <workbookView xWindow="2830" yWindow="2830" windowWidth="14400" windowHeight="8190" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,106 +44,106 @@
     <t>Ticker</t>
   </si>
   <si>
-    <t>AI.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IFX.DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LONN.SW</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HOLN.SW</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ENGI.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAN.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALC.SW</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIO.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ADS.DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AMS.MC</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> UCB.BR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DG.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HEI.DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAND.ST</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ASM.AS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOKIA.HE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HLN.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SGO.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ML.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> KNEBV.HE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DSY.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HEN3.DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EQNR.OL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ENI.MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VWS.CP</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> STMPA.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HLMA.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MRK.DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> INF.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ESSITY-B.ST</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AAL.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DSM.AS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SDZ.SW</t>
-  </si>
-  <si>
-    <t>TSLA</t>
+    <t>IFNNY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TSLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AIQUY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LZAGY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HCMLY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ENGIY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SNY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ALC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ADDYY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AMADY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> UCBJY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VCISY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HDELY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SDVKY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ASMIY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NOK</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HLN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SGOFY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MGDDY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KNYJY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DASTY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HENKY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EQNR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> E</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VWDRY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> STM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HLMAF</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MKKGY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> IFJPY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ESSYY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NGLOY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DSNMY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SDZNY</t>
   </si>
 </sst>
 </file>
@@ -525,172 +525,172 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -699,20 +699,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -904,14 +904,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -923,6 +915,14 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://record909-my.sharepoint.com/personal/amr_sanad_re-cord_org/Documents/amr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19582FC5-95DB-4811-A2C1-F90FC952C57C}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F236671-C974-5752-A55E-6BEBC924AA0C}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
   </bookViews>
@@ -44,106 +44,106 @@
     <t>Ticker</t>
   </si>
   <si>
-    <t>IFNNY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TSLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AIQUY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LZAGY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HCMLY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ENGIY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SNY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALC</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ADDYY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AMADY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> UCBJY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VCISY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HDELY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SDVKY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ASMIY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOK</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HLN</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SGOFY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MGDDY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> KNYJY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DASTY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HENKY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EQNR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> E</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VWDRY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> STM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HLMAF</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MKKGY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IFJPY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ESSYY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NGLOY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DSNMY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SDZNY</t>
+    <t>AI.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> IFX.DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LONN.SW</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HOLN.SW</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ENGI.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SAN.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ALC.SW</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RIO.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ADS.DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AMS.MC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> UCB.BR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DG.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HEI.DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SAND.ST</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ASM.AS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NOKIA.HE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HLN.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SGO.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ML.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KNEBV.HE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DSY.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HEN3.DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EQNR.OL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ENI.MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VWS.CP</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> STMPA.PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HLMA.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MRK.DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> INF.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ESSITY-B.ST</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AAL.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DSM.AS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SDZ.SW</t>
+  </si>
+  <si>
+    <t>TSLA</t>
   </si>
 </sst>
 </file>
@@ -196,6 +196,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -525,172 +529,172 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -699,23 +703,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008AE3B3EDB90C1F40A59126B8CDC80D43" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d1058065e7477b9d5077457695db4452">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="08f2707e77d3c1c984faf87c8023d60a" ns3:_="">
     <xsd:import namespace="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
@@ -903,31 +890,24 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B8DD49-09CB-47DE-8251-F67EE41634AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -943,4 +923,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://record909-my.sharepoint.com/personal/amr_sanad_re-cord_org/Documents/amr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F236671-C974-5752-A55E-6BEBC924AA0C}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EBD53FC-1D95-49E1-BBA5-248D3838E4AB}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
   </bookViews>
@@ -44,106 +44,106 @@
     <t>Ticker</t>
   </si>
   <si>
-    <t>AI.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IFX.DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> LONN.SW</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HOLN.SW</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ENGI.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAN.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALC.SW</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RIO.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ADS.DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AMS.MC</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> UCB.BR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DG.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HEI.DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SAND.ST</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ASM.AS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NOKIA.HE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HLN.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SGO.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ML.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> KNEBV.HE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DSY.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HEN3.DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EQNR.OL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ENI.MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VWS.CP</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> STMPA.PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> HLMA.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MRK.DE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> INF.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ESSITY-B.ST</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AAL.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DSM.AS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SDZ.SW</t>
-  </si>
-  <si>
     <t>TSLA</t>
+  </si>
+  <si>
+    <t>IFX.DE</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>LONN.SW</t>
+  </si>
+  <si>
+    <t>HOLN.SW</t>
+  </si>
+  <si>
+    <t>ENGI.PA</t>
+  </si>
+  <si>
+    <t>SAN</t>
+  </si>
+  <si>
+    <t>ALC</t>
+  </si>
+  <si>
+    <t>RIO</t>
+  </si>
+  <si>
+    <t>ADSK</t>
+  </si>
+  <si>
+    <t>AMSC</t>
+  </si>
+  <si>
+    <t>UCB</t>
+  </si>
+  <si>
+    <t>DG</t>
+  </si>
+  <si>
+    <t>HEI</t>
+  </si>
+  <si>
+    <t>SNDK</t>
+  </si>
+  <si>
+    <t>ASML</t>
+  </si>
+  <si>
+    <t>NOK</t>
+  </si>
+  <si>
+    <t>HLN</t>
+  </si>
+  <si>
+    <t>SGO.PA</t>
+  </si>
+  <si>
+    <t>MLI</t>
+  </si>
+  <si>
+    <t>KNEBV.HE</t>
+  </si>
+  <si>
+    <t>DSY.PA</t>
+  </si>
+  <si>
+    <t>HEN3.DE</t>
+  </si>
+  <si>
+    <t>EQNR</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>VWS.CP</t>
+  </si>
+  <si>
+    <t>STMPA.PA</t>
+  </si>
+  <si>
+    <t>HLMA.L</t>
+  </si>
+  <si>
+    <t>MRK</t>
+  </si>
+  <si>
+    <t>FIS</t>
+  </si>
+  <si>
+    <t>ESSITY-B.ST</t>
+  </si>
+  <si>
+    <t>AAL</t>
+  </si>
+  <si>
+    <t>DSM</t>
+  </si>
+  <si>
+    <t>SDZ.SW</t>
   </si>
 </sst>
 </file>
@@ -196,10 +196,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -534,167 +530,167 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -703,6 +699,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008AE3B3EDB90C1F40A59126B8CDC80D43" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d1058065e7477b9d5077457695db4452">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="08f2707e77d3c1c984faf87c8023d60a" ns3:_="">
     <xsd:import namespace="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
@@ -890,24 +903,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B8DD49-09CB-47DE-8251-F67EE41634AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -923,28 +943,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://record909-my.sharepoint.com/personal/amr_sanad_re-cord_org/Documents/amr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EBD53FC-1D95-49E1-BBA5-248D3838E4AB}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6958A39-B887-4F6F-877D-B1D77C380CD6}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Ticker</t>
   </si>
@@ -144,6 +144,24 @@
   </si>
   <si>
     <t>SDZ.SW</t>
+  </si>
+  <si>
+    <t>WM</t>
+  </si>
+  <si>
+    <t>RACE</t>
+  </si>
+  <si>
+    <t>CEG</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>DHI</t>
+  </si>
+  <si>
+    <t>AZO</t>
   </si>
 </sst>
 </file>
@@ -515,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE15FF02-FA5F-4B38-AD88-014FE2510093}">
-  <dimension ref="A1:A35"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.75">
@@ -693,26 +711,56 @@
         <v>34</v>
       </c>
     </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -904,14 +952,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -923,6 +963,14 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://record909-my.sharepoint.com/personal/amr_sanad_re-cord_org/Documents/amr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6958A39-B887-4F6F-877D-B1D77C380CD6}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F86F1F44-E680-4B56-B8B4-451E32C0AC58}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
   </bookViews>
@@ -39,32 +39,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>IFX.DE</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>LONN.SW</t>
-  </si>
-  <si>
     <t>HOLN.SW</t>
   </si>
   <si>
-    <t>ENGI.PA</t>
-  </si>
-  <si>
-    <t>SAN</t>
-  </si>
-  <si>
     <t>ALC</t>
   </si>
   <si>
@@ -74,21 +56,9 @@
     <t>ADSK</t>
   </si>
   <si>
-    <t>AMSC</t>
-  </si>
-  <si>
-    <t>UCB</t>
-  </si>
-  <si>
-    <t>DG</t>
-  </si>
-  <si>
     <t>HEI</t>
   </si>
   <si>
-    <t>SNDK</t>
-  </si>
-  <si>
     <t>ASML</t>
   </si>
   <si>
@@ -98,9 +68,6 @@
     <t>HLN</t>
   </si>
   <si>
-    <t>SGO.PA</t>
-  </si>
-  <si>
     <t>MLI</t>
   </si>
   <si>
@@ -110,58 +77,31 @@
     <t>DSY.PA</t>
   </si>
   <si>
-    <t>HEN3.DE</t>
-  </si>
-  <si>
-    <t>EQNR</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>VWS.CP</t>
-  </si>
-  <si>
     <t>STMPA.PA</t>
   </si>
   <si>
-    <t>HLMA.L</t>
-  </si>
-  <si>
-    <t>MRK</t>
-  </si>
-  <si>
-    <t>FIS</t>
-  </si>
-  <si>
     <t>ESSITY-B.ST</t>
   </si>
   <si>
-    <t>AAL</t>
-  </si>
-  <si>
-    <t>DSM</t>
-  </si>
-  <si>
-    <t>SDZ.SW</t>
-  </si>
-  <si>
-    <t>WM</t>
-  </si>
-  <si>
     <t>RACE</t>
   </si>
   <si>
     <t>CEG</t>
   </si>
   <si>
-    <t>VST</t>
-  </si>
-  <si>
     <t>DHI</t>
   </si>
   <si>
-    <t>AZO</t>
+    <t>UCB.bru</t>
+  </si>
+  <si>
+    <t>DG.par</t>
+  </si>
+  <si>
+    <t>VWSB.DE</t>
+  </si>
+  <si>
+    <t>DSFIR.AMS</t>
   </si>
 </sst>
 </file>
@@ -533,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE15FF02-FA5F-4B38-AD88-014FE2510093}">
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.75">
@@ -543,12 +483,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.75">
@@ -563,182 +503,82 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A34" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A39" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A40" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A41" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -747,20 +587,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -952,6 +792,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -963,14 +811,6 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://record909-my.sharepoint.com/personal/amr_sanad_re-cord_org/Documents/amr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F86F1F44-E680-4B56-B8B4-451E32C0AC58}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2D4651E-77F8-43FE-9929-B7F13D9B74D9}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Ticker</t>
   </si>
@@ -47,42 +47,12 @@
     <t>HOLN.SW</t>
   </si>
   <si>
-    <t>ALC</t>
-  </si>
-  <si>
-    <t>RIO</t>
-  </si>
-  <si>
     <t>ADSK</t>
   </si>
   <si>
-    <t>HEI</t>
-  </si>
-  <si>
     <t>ASML</t>
   </si>
   <si>
-    <t>NOK</t>
-  </si>
-  <si>
-    <t>HLN</t>
-  </si>
-  <si>
-    <t>MLI</t>
-  </si>
-  <si>
-    <t>KNEBV.HE</t>
-  </si>
-  <si>
-    <t>DSY.PA</t>
-  </si>
-  <si>
-    <t>STMPA.PA</t>
-  </si>
-  <si>
-    <t>ESSITY-B.ST</t>
-  </si>
-  <si>
     <t>RACE</t>
   </si>
   <si>
@@ -102,6 +72,27 @@
   </si>
   <si>
     <t>DSFIR.AMS</t>
+  </si>
+  <si>
+    <t>PODD</t>
+  </si>
+  <si>
+    <t>2GB.XETR</t>
+  </si>
+  <si>
+    <t>FIX</t>
+  </si>
+  <si>
+    <t>BY6.GETTEX</t>
+  </si>
+  <si>
+    <t>XOM</t>
+  </si>
+  <si>
+    <t>CYR.de</t>
+  </si>
+  <si>
+    <t>SUN.SW</t>
   </si>
 </sst>
 </file>
@@ -473,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE15FF02-FA5F-4B38-AD88-014FE2510093}">
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.75">
@@ -493,92 +484,77 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://record909-my.sharepoint.com/personal/amr_sanad_re-cord_org/Documents/amr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2D4651E-77F8-43FE-9929-B7F13D9B74D9}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{758ED8EE-0BAB-4D5B-A53B-7D3929FDB087}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
   </bookViews>
@@ -62,37 +62,37 @@
     <t>DHI</t>
   </si>
   <si>
-    <t>UCB.bru</t>
-  </si>
-  <si>
-    <t>DG.par</t>
-  </si>
-  <si>
     <t>VWSB.DE</t>
   </si>
   <si>
-    <t>DSFIR.AMS</t>
-  </si>
-  <si>
     <t>PODD</t>
   </si>
   <si>
-    <t>2GB.XETR</t>
-  </si>
-  <si>
     <t>FIX</t>
   </si>
   <si>
-    <t>BY6.GETTEX</t>
-  </si>
-  <si>
-    <t>XOM</t>
-  </si>
-  <si>
     <t>CYR.de</t>
   </si>
   <si>
     <t>SUN.SW</t>
+  </si>
+  <si>
+    <t>BYDDY</t>
+  </si>
+  <si>
+    <t>2GB.de</t>
+  </si>
+  <si>
+    <t>DSFIR.AS</t>
+  </si>
+  <si>
+    <t>UCB.br</t>
+  </si>
+  <si>
+    <t>DG.pa</t>
+  </si>
+  <si>
+    <t>XONA.de</t>
   </si>
 </sst>
 </file>
@@ -145,6 +145,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -484,12 +488,12 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.75">
@@ -499,12 +503,12 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.75">
@@ -524,37 +528,37 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://record909-my.sharepoint.com/personal/amr_sanad_re-cord_org/Documents/amr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{758ED8EE-0BAB-4D5B-A53B-7D3929FDB087}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B089D839-7D10-4C57-BC52-1FB268DBDF9B}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Ticker</t>
   </si>
@@ -81,15 +81,6 @@
   </si>
   <si>
     <t>2GB.de</t>
-  </si>
-  <si>
-    <t>DSFIR.AS</t>
-  </si>
-  <si>
-    <t>UCB.br</t>
-  </si>
-  <si>
-    <t>DG.pa</t>
   </si>
   <si>
     <t>XONA.de</t>
@@ -145,10 +136,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -468,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE15FF02-FA5F-4B38-AD88-014FE2510093}">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.75">
@@ -488,76 +475,61 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A18" t="s">
         <v>11</v>
       </c>
     </row>
@@ -567,23 +539,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008AE3B3EDB90C1F40A59126B8CDC80D43" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d1058065e7477b9d5077457695db4452">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="08f2707e77d3c1c984faf87c8023d60a" ns3:_="">
     <xsd:import namespace="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
@@ -771,31 +726,24 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B8DD49-09CB-47DE-8251-F67EE41634AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -811,4 +759,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://record909-my.sharepoint.com/personal/amr_sanad_re-cord_org/Documents/amr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B089D839-7D10-4C57-BC52-1FB268DBDF9B}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B538C019-63CB-450B-97FF-E5D977814DF8}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Ticker</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>XONA.de</t>
+  </si>
+  <si>
+    <t>XIACF</t>
+  </si>
+  <si>
+    <t>3cp.F</t>
   </si>
 </sst>
 </file>
@@ -455,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE15FF02-FA5F-4B38-AD88-014FE2510093}">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.75">
@@ -533,12 +539,30 @@
         <v>11</v>
       </c>
     </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008AE3B3EDB90C1F40A59126B8CDC80D43" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d1058065e7477b9d5077457695db4452">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="08f2707e77d3c1c984faf87c8023d60a" ns3:_="">
     <xsd:import namespace="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
@@ -726,14 +750,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -744,6 +760,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B8DD49-09CB-47DE-8251-F67EE41634AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -761,22 +793,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
   <ds:schemaRefs>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://record909-my.sharepoint.com/personal/amr_sanad_re-cord_org/Documents/amr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B538C019-63CB-450B-97FF-E5D977814DF8}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4765C855-6887-4440-BA1F-FA931A4C567F}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Ticker</t>
   </si>
@@ -90,6 +90,33 @@
   </si>
   <si>
     <t>3cp.F</t>
+  </si>
+  <si>
+    <t>JUFO.CA</t>
+  </si>
+  <si>
+    <t>CPCI.CA</t>
+  </si>
+  <si>
+    <t>SKPC.CA</t>
+  </si>
+  <si>
+    <t>EFID.CA</t>
+  </si>
+  <si>
+    <t>PHDC.CA</t>
+  </si>
+  <si>
+    <t>MOSC.CA</t>
+  </si>
+  <si>
+    <t>AXPH.CA</t>
+  </si>
+  <si>
+    <t>EGAL.CA</t>
+  </si>
+  <si>
+    <t>ISMQ.CA</t>
   </si>
 </sst>
 </file>
@@ -125,8 +152,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE15FF02-FA5F-4B38-AD88-014FE2510093}">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.75">
@@ -549,20 +579,57 @@
         <v>16</v>
       </c>
     </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008AE3B3EDB90C1F40A59126B8CDC80D43" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d1058065e7477b9d5077457695db4452">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="08f2707e77d3c1c984faf87c8023d60a" ns3:_="">
     <xsd:import namespace="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
@@ -750,6 +817,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -760,22 +835,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B8DD49-09CB-47DE-8251-F67EE41634AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -793,6 +852,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5F5C41-6460-4DB5-BF58-CC7385BA2AA7}">
   <ds:schemaRefs>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://record909-my.sharepoint.com/personal/amr_sanad_re-cord_org/Documents/amr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4765C855-6887-4440-BA1F-FA931A4C567F}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="8_{9DC957E0-3F63-4619-A2B1-EAFF9133C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5617FEDB-7411-4344-8797-C013813D158E}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{E2703A95-F99F-4E35-9D76-557C875699E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Ticker</t>
   </si>
@@ -117,6 +117,15 @@
   </si>
   <si>
     <t>ISMQ.CA</t>
+  </si>
+  <si>
+    <t>EDFM.CA</t>
+  </si>
+  <si>
+    <t>egas.ca</t>
+  </si>
+  <si>
+    <t>smci</t>
   </si>
 </sst>
 </file>
@@ -491,137 +500,152 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE15FF02-FA5F-4B38-AD88-014FE2510093}">
-  <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -630,6 +654,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008AE3B3EDB90C1F40A59126B8CDC80D43" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d1058065e7477b9d5077457695db4452">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="08f2707e77d3c1c984faf87c8023d60a" ns3:_="">
     <xsd:import namespace="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
@@ -817,14 +849,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -835,35 +859,24 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B8DD49-09CB-47DE-8251-F67EE41634AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED50DB0B-DC84-43AD-A4C8-C82A90B88577}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="1f5e9890-80e7-4fee-9ea3-d0d67105bcb2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
